--- a/artfynd/A 35939-2024 artfynd.xlsx
+++ b/artfynd/A 35939-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120071407</v>
+        <v>120071479</v>
       </c>
       <c r="B2" t="n">
-        <v>90582</v>
+        <v>57463</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597133</v>
+        <v>597066</v>
       </c>
       <c r="R2" t="n">
-        <v>6383299</v>
+        <v>6383317</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -780,7 +781,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120071479</v>
+        <v>120071407</v>
       </c>
       <c r="B3" t="n">
-        <v>57463</v>
+        <v>90582</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,35 +815,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -851,13 +850,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597066</v>
+        <v>597133</v>
       </c>
       <c r="R3" t="n">
-        <v>6383317</v>
+        <v>6383299</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -905,6 +904,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120071390</v>
+        <v>120071417</v>
       </c>
       <c r="B4" t="n">
-        <v>91884</v>
+        <v>94681</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,38 +935,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -974,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597024</v>
+        <v>597134</v>
       </c>
       <c r="R4" t="n">
-        <v>6383350</v>
+        <v>6383244</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1047,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120071417</v>
+        <v>120071390</v>
       </c>
       <c r="B5" t="n">
-        <v>94681</v>
+        <v>91884</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,31 +1052,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597134</v>
+        <v>597024</v>
       </c>
       <c r="R5" t="n">
-        <v>6383244</v>
+        <v>6383350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35939-2024 artfynd.xlsx
+++ b/artfynd/A 35939-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120071479</v>
+        <v>120071417</v>
       </c>
       <c r="B2" t="n">
-        <v>57463</v>
+        <v>94681</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597066</v>
+        <v>597134</v>
       </c>
       <c r="R2" t="n">
-        <v>6383317</v>
+        <v>6383244</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,6 +773,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120071407</v>
+        <v>120071390</v>
       </c>
       <c r="B3" t="n">
-        <v>90582</v>
+        <v>91884</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -850,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597133</v>
+        <v>597024</v>
       </c>
       <c r="R3" t="n">
-        <v>6383299</v>
+        <v>6383350</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -923,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120071417</v>
+        <v>120071479</v>
       </c>
       <c r="B4" t="n">
-        <v>94681</v>
+        <v>57463</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,31 +928,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -967,13 +968,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597134</v>
+        <v>597066</v>
       </c>
       <c r="R4" t="n">
-        <v>6383244</v>
+        <v>6383317</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1021,7 +1022,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1040,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120071390</v>
+        <v>120071407</v>
       </c>
       <c r="B5" t="n">
-        <v>91884</v>
+        <v>90582</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,21 +1056,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597024</v>
+        <v>597133</v>
       </c>
       <c r="R5" t="n">
-        <v>6383350</v>
+        <v>6383299</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35939-2024 artfynd.xlsx
+++ b/artfynd/A 35939-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120071417</v>
+        <v>120071390</v>
       </c>
       <c r="B2" t="n">
-        <v>94681</v>
+        <v>91884</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597134</v>
+        <v>597024</v>
       </c>
       <c r="R2" t="n">
-        <v>6383244</v>
+        <v>6383350</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -792,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120071390</v>
+        <v>120071417</v>
       </c>
       <c r="B3" t="n">
-        <v>91884</v>
+        <v>94681</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +811,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597024</v>
+        <v>597134</v>
       </c>
       <c r="R3" t="n">
-        <v>6383350</v>
+        <v>6383244</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 35939-2024 artfynd.xlsx
+++ b/artfynd/A 35939-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120071390</v>
+        <v>120071407</v>
       </c>
       <c r="B2" t="n">
-        <v>91884</v>
+        <v>90600</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597024</v>
+        <v>597133</v>
       </c>
       <c r="R2" t="n">
-        <v>6383350</v>
+        <v>6383299</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120071417</v>
+        <v>120071390</v>
       </c>
       <c r="B3" t="n">
-        <v>94681</v>
+        <v>91902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,31 +811,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597134</v>
+        <v>597024</v>
       </c>
       <c r="R3" t="n">
-        <v>6383244</v>
+        <v>6383350</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -916,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120071479</v>
+        <v>120071417</v>
       </c>
       <c r="B4" t="n">
-        <v>57463</v>
+        <v>94704</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,39 +935,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -968,13 +967,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597066</v>
+        <v>597134</v>
       </c>
       <c r="R4" t="n">
-        <v>6383317</v>
+        <v>6383244</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1022,6 +1021,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1040,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120071407</v>
+        <v>120071479</v>
       </c>
       <c r="B5" t="n">
-        <v>90582</v>
+        <v>57473</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,34 +1056,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1091,13 +1092,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597133</v>
+        <v>597066</v>
       </c>
       <c r="R5" t="n">
-        <v>6383299</v>
+        <v>6383317</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1145,7 +1146,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35939-2024 artfynd.xlsx
+++ b/artfynd/A 35939-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120071407</v>
+        <v>120071390</v>
       </c>
       <c r="B2" t="n">
-        <v>90600</v>
+        <v>91902</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597133</v>
+        <v>597024</v>
       </c>
       <c r="R2" t="n">
-        <v>6383299</v>
+        <v>6383350</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120071390</v>
+        <v>120071479</v>
       </c>
       <c r="B3" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,34 +815,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -850,13 +851,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597024</v>
+        <v>597066</v>
       </c>
       <c r="R3" t="n">
-        <v>6383350</v>
+        <v>6383317</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -904,7 +905,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1040,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120071479</v>
+        <v>120071407</v>
       </c>
       <c r="B5" t="n">
-        <v>57473</v>
+        <v>90600</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,35 +1056,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1092,13 +1091,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597066</v>
+        <v>597133</v>
       </c>
       <c r="R5" t="n">
-        <v>6383317</v>
+        <v>6383299</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1146,6 +1145,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35939-2024 artfynd.xlsx
+++ b/artfynd/A 35939-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120071390</v>
+        <v>120071479</v>
       </c>
       <c r="B2" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597024</v>
+        <v>597066</v>
       </c>
       <c r="R2" t="n">
-        <v>6383350</v>
+        <v>6383317</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -780,7 +781,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120071479</v>
+        <v>120071390</v>
       </c>
       <c r="B3" t="n">
-        <v>57473</v>
+        <v>91902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,35 +815,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -851,13 +850,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597066</v>
+        <v>597024</v>
       </c>
       <c r="R3" t="n">
-        <v>6383317</v>
+        <v>6383350</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -905,6 +904,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120071417</v>
+        <v>120071407</v>
       </c>
       <c r="B4" t="n">
-        <v>94704</v>
+        <v>90600</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,31 +935,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -967,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597134</v>
+        <v>597133</v>
       </c>
       <c r="R4" t="n">
-        <v>6383244</v>
+        <v>6383299</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1040,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120071407</v>
+        <v>120071417</v>
       </c>
       <c r="B5" t="n">
-        <v>90600</v>
+        <v>94704</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,38 +1059,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597133</v>
+        <v>597134</v>
       </c>
       <c r="R5" t="n">
-        <v>6383299</v>
+        <v>6383244</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35939-2024 artfynd.xlsx
+++ b/artfynd/A 35939-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120071479</v>
+        <v>120071417</v>
       </c>
       <c r="B2" t="n">
-        <v>57473</v>
+        <v>94704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597066</v>
+        <v>597134</v>
       </c>
       <c r="R2" t="n">
-        <v>6383317</v>
+        <v>6383244</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,6 +773,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -923,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120071407</v>
+        <v>120071479</v>
       </c>
       <c r="B4" t="n">
-        <v>90600</v>
+        <v>57473</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,34 +932,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -974,13 +968,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597133</v>
+        <v>597066</v>
       </c>
       <c r="R4" t="n">
-        <v>6383299</v>
+        <v>6383317</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1028,7 +1022,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1047,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120071417</v>
+        <v>120071407</v>
       </c>
       <c r="B5" t="n">
-        <v>94704</v>
+        <v>90600</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,31 +1052,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597134</v>
+        <v>597133</v>
       </c>
       <c r="R5" t="n">
-        <v>6383244</v>
+        <v>6383299</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35939-2024 artfynd.xlsx
+++ b/artfynd/A 35939-2024 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120071390</v>
+        <v>120071407</v>
       </c>
       <c r="B3" t="n">
-        <v>91902</v>
+        <v>90600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597024</v>
+        <v>597133</v>
       </c>
       <c r="R3" t="n">
-        <v>6383350</v>
+        <v>6383299</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120071479</v>
+        <v>120071390</v>
       </c>
       <c r="B4" t="n">
-        <v>57473</v>
+        <v>91902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,35 +932,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -968,13 +967,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597066</v>
+        <v>597024</v>
       </c>
       <c r="R4" t="n">
-        <v>6383317</v>
+        <v>6383350</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1022,6 +1021,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1040,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120071407</v>
+        <v>120071479</v>
       </c>
       <c r="B5" t="n">
-        <v>90600</v>
+        <v>57473</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,34 +1056,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1091,13 +1092,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597133</v>
+        <v>597066</v>
       </c>
       <c r="R5" t="n">
-        <v>6383299</v>
+        <v>6383317</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1145,7 +1146,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35939-2024 artfynd.xlsx
+++ b/artfynd/A 35939-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120071417</v>
+        <v>120071390</v>
       </c>
       <c r="B2" t="n">
-        <v>94704</v>
+        <v>91902</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597134</v>
+        <v>597024</v>
       </c>
       <c r="R2" t="n">
-        <v>6383244</v>
+        <v>6383350</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -792,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120071407</v>
+        <v>120071417</v>
       </c>
       <c r="B3" t="n">
-        <v>90600</v>
+        <v>94704</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +811,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597133</v>
+        <v>597134</v>
       </c>
       <c r="R3" t="n">
-        <v>6383299</v>
+        <v>6383244</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120071390</v>
+        <v>120071479</v>
       </c>
       <c r="B4" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,34 +932,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -967,13 +968,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597024</v>
+        <v>597066</v>
       </c>
       <c r="R4" t="n">
-        <v>6383350</v>
+        <v>6383317</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1021,7 +1022,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1040,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120071479</v>
+        <v>120071407</v>
       </c>
       <c r="B5" t="n">
-        <v>57473</v>
+        <v>90600</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,35 +1056,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1092,13 +1091,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597066</v>
+        <v>597133</v>
       </c>
       <c r="R5" t="n">
-        <v>6383317</v>
+        <v>6383299</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1146,6 +1145,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35939-2024 artfynd.xlsx
+++ b/artfynd/A 35939-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120071390</v>
+        <v>120071417</v>
       </c>
       <c r="B2" t="n">
-        <v>91902</v>
+        <v>94704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597024</v>
+        <v>597134</v>
       </c>
       <c r="R2" t="n">
-        <v>6383350</v>
+        <v>6383244</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -799,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120071417</v>
+        <v>120071407</v>
       </c>
       <c r="B3" t="n">
-        <v>94704</v>
+        <v>90600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,31 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597134</v>
+        <v>597133</v>
       </c>
       <c r="R3" t="n">
-        <v>6383244</v>
+        <v>6383299</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1040,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120071407</v>
+        <v>120071390</v>
       </c>
       <c r="B5" t="n">
-        <v>90600</v>
+        <v>91902</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,21 +1056,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597133</v>
+        <v>597024</v>
       </c>
       <c r="R5" t="n">
-        <v>6383299</v>
+        <v>6383350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35939-2024 artfynd.xlsx
+++ b/artfynd/A 35939-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>120071417</v>
       </c>
       <c r="B2" t="n">
-        <v>94704</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120071479</v>
+        <v>120071407</v>
       </c>
       <c r="B3" t="n">
-        <v>57473</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,35 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597066</v>
+        <v>597133</v>
       </c>
       <c r="R3" t="n">
-        <v>6383317</v>
+        <v>6383299</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -898,6 +887,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -916,15 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120071407</v>
+        <v>120071479</v>
       </c>
       <c r="B4" t="n">
-        <v>90600</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,34 +917,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -967,13 +953,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597133</v>
+        <v>597066</v>
       </c>
       <c r="R4" t="n">
-        <v>6383299</v>
+        <v>6383317</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1021,7 +1007,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1037,130 +1022,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>120071390</v>
-      </c>
-      <c r="B5" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>A 35939, Skälö, Sm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>597024</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6383350</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Västrum</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
